--- a/sampleprojects/CorporateTax/excel/states/ME_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/ME_corp.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
   <si>
     <t>DT: Determine ME Filing Requirement</t>
   </si>
@@ -70,7 +70,7 @@
     <t>Meets economic nexus threshold (factor presence standards); result.me_gross_receipts is greater than or equal to result.me_economic_nexus_threshold</t>
   </si>
   <si>
-    <t>result.me_gross_receipts &gt;= result.me_economic_nexus_threshold</t>
+    <t>me_result.gross_receipts &gt;= me_result.economic_nexus_threshold</t>
   </si>
   <si>
     <t>-</t>
@@ -85,7 +85,7 @@
     <t>Physical nexus - filing required</t>
   </si>
   <si>
-    <t>set result.me_has_nexus = true;</t>
+    <t>set me_result.has_nexus = true;</t>
   </si>
   <si>
     <t>X</t>
@@ -97,7 +97,7 @@
     <t>No nexus - no filing required</t>
   </si>
   <si>
-    <t>set result.me_has_nexus = false; set result.me_tax_liability = 0.0;</t>
+    <t>set me_result.has_nexus = false; set me_result.tax_liability = 0.0;</t>
   </si>
   <si>
     <t>DT: Calculate ME Income Adjustments</t>
@@ -115,19 +115,19 @@
     <t>Has Maine nexus</t>
   </si>
   <si>
-    <t>result.me_has_nexus is equal to true</t>
+    <t>me_result.has_nexus is equal to true</t>
   </si>
   <si>
     <t>Calculate Maine state additions and subtractions; Calculate state-specific income adjustments</t>
   </si>
   <si>
-    <t>set result.me_state_additions = 0.0; if result.me_section_199a_addback != 0.0 then set result.me_state_additions = result.me_state_additions + result.me_section_199a_addback; endif set result.me_state_subtractions = 0.0; if result.me_us_interest_income != 0.0 then set result.me_state_subtractions = result.me_state_subtractions + result.me_us_interest_income; endif if result.me_municipal_interest != 0.0 then set result.me_state_subtractions = result.me_state_subtractions + result.me_municipal_interest; endif add (("Maine additions: $" + string value of (result.me_state_additions)) + ", subtractions: $") + string value of (result.me_state_subtractions) to job.audit_trail;</t>
+    <t>set me_result.state_additions = 0.0; if me_result.section_199a_addback != 0.0 then set me_result.state_additions = me_result.state_additions + me_result.section_199a_addback; endif set me_result.state_subtractions = 0.0; if me_result.us_interest_income != 0.0 then set me_result.state_subtractions = me_result.state_subtractions + me_result.us_interest_income; endif if me_result.municipal_interest != 0.0 then set me_result.state_subtractions = me_result.state_subtractions + me_result.municipal_interest; endif add (("Maine additions: $" + string value of (me_result.state_additions)) + ", subtractions: $") + string value of (me_result.state_subtractions) to job.audit_trail;</t>
   </si>
   <si>
     <t>No nexus - no adjustments</t>
   </si>
   <si>
-    <t>set result.me_state_additions = 0.0; set result.me_state_subtractions = 0.0;</t>
+    <t>set me_result.state_additions = 0.0; set me_result.state_subtractions = 0.0;</t>
   </si>
   <si>
     <t>DT: Calculate ME State Tax</t>
@@ -145,19 +145,19 @@
     <t>Has positive taxable income; result.me_apportioned_income is greater than 0</t>
   </si>
   <si>
-    <t>result.me_apportioned_income &gt; 0.0</t>
+    <t>me_result.apportioned_income &gt; 0.0</t>
   </si>
   <si>
     <t>Calculate Maine corporate tax (graduated rates); Apply Maine graduated rates (3.5%, 7.5%, 8.3%, 8.93%)</t>
   </si>
   <si>
-    <t>set result.me_taxable_income = the maximum of (result.me_apportioned_income + result.me_state_additions - result.me_state_subtractions) and (0.0); set result.me_tier1_tax = (the minimum of (result.me_taxable_income) and (350000.0)) * result.me_corp_tax_rate_tier1; set result.me_tier2_tax = 0.0; set result.me_tier3_tax = 0.0; set result.me_tier4_tax = 0.0; if result.me_taxable_income &gt; 350000.0 then set result.me_tier2_tax = ((the minimum of (result.me_taxable_income) and (1050000.0)) - 350000.0) * result.me_corp_tax_rate_tier2; endif if result.me_taxable_income &gt; 1050000.0 then set result.me_tier3_tax = ((the minimum of (result.me_taxable_income) and (3500000.0)) - 1050000.0) * result.me_corp_tax_rate_tier3; endif if result.me_taxable_income &gt; 3500000.0 then set result.me_tier4_tax = (result.me_taxable_income - 3500000.0) * result.me_corp_tax_rate_tier4; endif set result.me_tax_liability = the maximum of (result.me_tier1_tax + result.me_tier2_tax + result.me_tier3_tax + result.me_tier4_tax - result.me_state_credits) and (0.0); set result.me_refund_or_owed = result.me_estimated_payments - result.me_tax_liability; add "Maine taxable income: $" + string value of (result.me_taxable_income) to job.audit_trail; add "Maine tax liability (graduated rates 3.5%-8.93%): $" + string value of (result.me_tax_liability) to job.audit_trail;</t>
+    <t>set me_result.taxable_income = the maximum of (me_result.apportioned_income + me_result.state_additions - me_result.state_subtractions) and (0.0); set me_result.tier1_tax = (the minimum of (me_result.taxable_income) and (350000.0)) * me_result.corp_tax_rate_tier1; set me_result.tier2_tax = 0.0; set me_result.tier3_tax = 0.0; set me_result.tier4_tax = 0.0; if me_result.taxable_income &gt; 350000.0 then set me_result.tier2_tax = ((the minimum of (me_result.taxable_income) and (1050000.0)) - 350000.0) * me_result.corp_tax_rate_tier2; endif if me_result.taxable_income &gt; 1050000.0 then set me_result.tier3_tax = ((the minimum of (me_result.taxable_income) and (3500000.0)) - 1050000.0) * me_result.corp_tax_rate_tier3; endif if me_result.taxable_income &gt; 3500000.0 then set me_result.tier4_tax = (me_result.taxable_income - 3500000.0) * me_result.corp_tax_rate_tier4; endif set me_result.tax_liability = the maximum of (me_result.tier1_tax + me_result.tier2_tax + me_result.tier3_tax + me_result.tier4_tax - me_result.state_credits) and (0.0); set me_result.refund_or_owed = me_result.estimated_payments - me_result.tax_liability; add "Maine taxable income: $" + string value of (me_result.taxable_income) to job.audit_trail; add "Maine tax liability (graduated rates 3.5%-8.93%): $" + string value of (me_result.tax_liability) to job.audit_trail;</t>
   </si>
   <si>
     <t>No taxable income - no tax liability</t>
   </si>
   <si>
-    <t>set result.me_taxable_income = 0.0; set result.me_tax_liability = 0.0;</t>
+    <t>set me_result.taxable_income = 0.0; set me_result.tax_liability = 0.0;</t>
   </si>
   <si>
     <t>No nexus - no tax liability</t>
@@ -205,10 +205,10 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>apportionment</t>
-  </si>
-  <si>
-    <t>(16 attributes)</t>
+    <t>me_apportionment</t>
+  </si>
+  <si>
+    <t>(1 attributes)</t>
   </si>
   <si>
     <t>apportionment_formula</t>
@@ -226,244 +226,127 @@
     <t>ME uses single-sales factor apportionment</t>
   </si>
   <si>
-    <t>economic_nexus_factor_percentage</t>
+    <t>me_result</t>
+  </si>
+  <si>
+    <t>(22 attributes)</t>
+  </si>
+  <si>
+    <t>apportioned_income</t>
   </si>
   <si>
     <t>double</t>
   </si>
   <si>
-    <t>0.25</t>
-  </si>
-  <si>
-    <t>ME economic nexus 25% factor presence threshold</t>
-  </si>
-  <si>
-    <t>economic_nexus_payroll_threshold</t>
-  </si>
-  <si>
-    <t>250000.0</t>
-  </si>
-  <si>
-    <t>ME economic nexus payroll threshold - $250,000</t>
-  </si>
-  <si>
-    <t>economic_nexus_property_threshold</t>
-  </si>
-  <si>
-    <t>ME economic nexus property threshold - $250,000</t>
-  </si>
-  <si>
-    <t>economic_nexus_sales_threshold</t>
-  </si>
-  <si>
-    <t>500000.0</t>
-  </si>
-  <si>
-    <t>ME economic nexus sales threshold - $500,000</t>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>Declared from decision-table usage; referenced by ME but never declared (campaign #948 Phase 1)</t>
+  </si>
+  <si>
+    <t>corp_tax_rate_tier1</t>
+  </si>
+  <si>
+    <t>0.035</t>
+  </si>
+  <si>
+    <t>1120ME instructions: 3.5% of adjusted federal taxable income up to $350,000</t>
+  </si>
+  <si>
+    <t>corp_tax_rate_tier2</t>
+  </si>
+  <si>
+    <t>0.0793</t>
+  </si>
+  <si>
+    <t>1120ME instructions: $12,250 plus 7.93% of the excess over $350,000</t>
+  </si>
+  <si>
+    <t>corp_tax_rate_tier3</t>
+  </si>
+  <si>
+    <t>0.0833</t>
+  </si>
+  <si>
+    <t>1120ME instructions: $67,760 plus 8.33% of the excess over $1,050,000</t>
+  </si>
+  <si>
+    <t>corp_tax_rate_tier4</t>
+  </si>
+  <si>
+    <t>0.0893</t>
+  </si>
+  <si>
+    <t>1120ME instructions: $271,845 plus 8.93% of the excess over $3,500,000</t>
+  </si>
+  <si>
+    <t>economic_nexus_threshold</t>
+  </si>
+  <si>
+    <t>estimated_payments</t>
+  </si>
+  <si>
+    <t>gross_receipts</t>
+  </si>
+  <si>
+    <t>has_nexus</t>
+  </si>
+  <si>
+    <t>boolean</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>municipal_interest</t>
+  </si>
+  <si>
+    <t>refund_or_owed</t>
+  </si>
+  <si>
+    <t>section_199a_addback</t>
   </si>
   <si>
     <t>state_additions</t>
   </si>
   <si>
-    <t>0.0</t>
-  </si>
-  <si>
-    <t>ME-specific additions: IRC 199A addback, bonus depreciation, etc.</t>
-  </si>
-  <si>
-    <t>state_code</t>
-  </si>
-  <si>
-    <t>ME</t>
-  </si>
-  <si>
-    <t>Maine state code</t>
-  </si>
-  <si>
     <t>state_credits</t>
   </si>
   <si>
-    <t>ME tax credits: Pine Tree Zone, R&amp;D, employment, etc.</t>
-  </si>
-  <si>
     <t>state_subtractions</t>
   </si>
   <si>
-    <t>ME-specific subtractions: federal interest, municipal interest, state NOL, etc.</t>
-  </si>
-  <si>
-    <t>tax_bracket_1</t>
-  </si>
-  <si>
-    <t>350000.0</t>
-  </si>
-  <si>
-    <t>ME tax bracket 1 threshold</t>
-  </si>
-  <si>
-    <t>tax_bracket_2</t>
-  </si>
-  <si>
-    <t>1050000.0</t>
-  </si>
-  <si>
-    <t>ME tax bracket 2 threshold</t>
-  </si>
-  <si>
-    <t>tax_bracket_3</t>
-  </si>
-  <si>
-    <t>3500000.0</t>
-  </si>
-  <si>
-    <t>ME tax bracket 3 threshold</t>
-  </si>
-  <si>
-    <t>tax_rate_tier1</t>
-  </si>
-  <si>
-    <t>0.035</t>
-  </si>
-  <si>
-    <t>ME tax rate tier 1 - 3.5% on income up to $350,000</t>
-  </si>
-  <si>
-    <t>tax_rate_tier2</t>
-  </si>
-  <si>
-    <t>0.075</t>
-  </si>
-  <si>
-    <t>ME tax rate tier 2 - 7.5% on income $350,000 to $1,050,000</t>
-  </si>
-  <si>
-    <t>tax_rate_tier3</t>
-  </si>
-  <si>
-    <t>0.083</t>
-  </si>
-  <si>
-    <t>ME tax rate tier 3 - 8.3% on income $1,050,000 to $3,500,000</t>
-  </si>
-  <si>
-    <t>tax_rate_tier4</t>
-  </si>
-  <si>
-    <t>0.0893</t>
-  </si>
-  <si>
-    <t>ME tax rate tier 4 - 8.93% on income over $3,500,000</t>
-  </si>
-  <si>
-    <t>result</t>
-  </si>
-  <si>
-    <t>(22 attributes)</t>
-  </si>
-  <si>
-    <t>me_apportioned_income</t>
-  </si>
-  <si>
-    <t>Declared from decision-table usage; referenced by ME but never declared (campaign #948 Phase 1)</t>
-  </si>
-  <si>
-    <t>me_corp_tax_rate_tier1</t>
-  </si>
-  <si>
-    <t>1120ME instructions: 3.5% of adjusted federal taxable income up to $350,000</t>
-  </si>
-  <si>
-    <t>me_corp_tax_rate_tier2</t>
-  </si>
-  <si>
-    <t>0.0793</t>
-  </si>
-  <si>
-    <t>1120ME instructions: $12,250 plus 7.93% of the excess over $350,000</t>
-  </si>
-  <si>
-    <t>me_corp_tax_rate_tier3</t>
-  </si>
-  <si>
-    <t>0.0833</t>
-  </si>
-  <si>
-    <t>1120ME instructions: $67,760 plus 8.33% of the excess over $1,050,000</t>
-  </si>
-  <si>
-    <t>me_corp_tax_rate_tier4</t>
-  </si>
-  <si>
-    <t>1120ME instructions: $271,845 plus 8.93% of the excess over $3,500,000</t>
-  </si>
-  <si>
-    <t>me_economic_nexus_threshold</t>
-  </si>
-  <si>
-    <t>me_estimated_payments</t>
-  </si>
-  <si>
-    <t>me_gross_receipts</t>
-  </si>
-  <si>
-    <t>me_has_nexus</t>
-  </si>
-  <si>
-    <t>boolean</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>me_municipal_interest</t>
-  </si>
-  <si>
-    <t>me_refund_or_owed</t>
-  </si>
-  <si>
-    <t>me_section_199a_addback</t>
-  </si>
-  <si>
-    <t>me_state_additions</t>
-  </si>
-  <si>
-    <t>me_state_credits</t>
-  </si>
-  <si>
-    <t>me_state_subtractions</t>
-  </si>
-  <si>
-    <t>me_tax_liability</t>
-  </si>
-  <si>
-    <t>me_taxable_income</t>
-  </si>
-  <si>
-    <t>me_tier1_tax</t>
+    <t>tax_liability</t>
+  </si>
+  <si>
+    <t>taxable_income</t>
+  </si>
+  <si>
+    <t>tier1_tax</t>
   </si>
   <si>
     <t>Per-bracket tax; tax from bracket 1 (3.5% up to $350,000). The original postfix held this in a fake local, which the EL authoring promoted to a real field (campaign #948).</t>
   </si>
   <si>
-    <t>me_tier2_tax</t>
+    <t>tier2_tax</t>
   </si>
   <si>
     <t>Per-bracket tax; tax from bracket 2 (7.93% of $350,001-$1,050,000). The original postfix held this in a fake local, which the EL authoring promoted to a real field (campaign #948).</t>
   </si>
   <si>
-    <t>me_tier3_tax</t>
+    <t>tier3_tax</t>
   </si>
   <si>
     <t>Per-bracket tax; tax from bracket 3 (8.33% of $1,050,001-$3,500,000). The original postfix held this in a fake local, which the EL authoring promoted to a real field (campaign #948).</t>
   </si>
   <si>
-    <t>me_tier4_tax</t>
+    <t>tier4_tax</t>
   </si>
   <si>
     <t>Per-bracket tax; tax from bracket 4 (8.93% over $3,500,000). The original postfix held this in a fake local, which the EL authoring promoted to a real field (campaign #948).</t>
   </si>
   <si>
-    <t>me_us_interest_income</t>
+    <t>us_interest_income</t>
   </si>
 </sst>
 </file>
@@ -2727,61 +2610,39 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="9" t="s">
+      <c r="A5" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="B5" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H5" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M5" s="8" t="s">
-        <v>8</v>
-      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>73</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>74</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>8</v>
@@ -2790,7 +2651,7 @@
         <v>67</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>8</v>
@@ -2813,16 +2674,16 @@
         <v>8</v>
       </c>
       <c r="B7" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>76</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>74</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>8</v>
@@ -2857,7 +2718,7 @@
         <v>78</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>8</v>
@@ -2898,7 +2759,7 @@
         <v>81</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>8</v>
@@ -2938,8 +2799,8 @@
       <c r="B10" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>65</v>
+      <c r="C10" s="11" t="s">
+        <v>72</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>8</v>
@@ -2980,13 +2841,13 @@
         <v>87</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>8</v>
@@ -2995,7 +2856,7 @@
         <v>67</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>8</v>
@@ -3018,16 +2879,16 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>8</v>
@@ -3036,7 +2897,7 @@
         <v>67</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>8</v>
@@ -3059,16 +2920,16 @@
         <v>8</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>8</v>
@@ -3077,7 +2938,7 @@
         <v>67</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="I13" s="8" t="s">
         <v>8</v>
@@ -3100,16 +2961,16 @@
         <v>8</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>70</v>
+        <v>90</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>91</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>8</v>
@@ -3118,7 +2979,7 @@
         <v>67</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>8</v>
@@ -3141,16 +3002,16 @@
         <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>8</v>
@@ -3159,7 +3020,7 @@
         <v>67</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="I15" s="8" t="s">
         <v>8</v>
@@ -3182,16 +3043,16 @@
         <v>8</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>8</v>
@@ -3200,7 +3061,7 @@
         <v>67</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>8</v>
@@ -3223,16 +3084,16 @@
         <v>8</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>8</v>
@@ -3241,7 +3102,7 @@
         <v>67</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="I17" s="8" t="s">
         <v>8</v>
@@ -3264,16 +3125,16 @@
         <v>8</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>8</v>
@@ -3282,7 +3143,7 @@
         <v>67</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>8</v>
@@ -3305,16 +3166,16 @@
         <v>8</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>8</v>
@@ -3323,7 +3184,7 @@
         <v>67</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="I19" s="8" t="s">
         <v>8</v>
@@ -3342,923 +3203,330 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
+      <c r="A20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="8" t="s">
         <v>8</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G21" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="8" t="s">
         <v>67</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L21" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M21" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="F22" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G22" s="8" t="s">
+      <c r="C23" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="H22" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K22" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L22" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M22" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G23" s="7" t="s">
+      <c r="H23" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="H23" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L23" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M23" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G24" s="8" t="s">
+      <c r="H24" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G25" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="H24" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K24" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L24" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M24" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G25" s="7" t="s">
+      <c r="H25" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M25" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="H25" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M25" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G26" s="8" t="s">
+      <c r="H26" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="H26" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M26" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>67</v>
-      </c>
       <c r="H27" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M27" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H28" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K28" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L28" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M28" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H29" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K29" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L29" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M29" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H30" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="I30" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J30" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K30" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L30" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M30" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H31" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K31" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L31" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M31" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H32" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K32" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L32" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M32" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H33" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J33" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K33" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L33" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M33" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H34" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="I34" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J34" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K34" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L34" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M34" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H35" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J35" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K35" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L35" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M35" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H36" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="I36" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J36" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K36" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L36" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M36" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G37" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H37" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="I37" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J37" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K37" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L37" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M37" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F38" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H38" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="I38" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J38" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K38" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L38" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M38" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H39" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="I39" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J39" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K39" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L39" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M39" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H40" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="I40" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J40" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K40" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L40" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M40" s="8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="H41" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="I41" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J41" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K41" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="L41" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="M41" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H42" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="I42" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J42" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="K42" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="L42" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M42" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M27" s="8" t="s">
         <v>8</v>
       </c>
     </row>
